--- a/data/dashboard_data.xlsx
+++ b/data/dashboard_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E491"/>
+  <dimension ref="A1:E493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,17 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Accounts Opened</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Accounts Closed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>Net Addition</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Accounts Opened</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Accounts Closed</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Pundri S.O</t>
+          <t>Product Wise A/C Report</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Punhana SO</t>
+          <t>Pundri S.O</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Punjabi Mohalla S.O</t>
+          <t>Punhana SO</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Purkhas SO</t>
+          <t>Punjabi Mohalla S.O</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Radaur S.O</t>
+          <t>Purkhas SO</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Railwary Road SO</t>
+          <t>Radaur S.O</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Railway Road Ambala City S.O</t>
+          <t>Railwary Road SO</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Raipur Rani S.O</t>
+          <t>Railway Road Ambala City S.O</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Rajound S.O</t>
+          <t>Raipur Rani S.O</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Ram BazarSonipat SO</t>
+          <t>Rajound S.O</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Ram Pura Olony S.O</t>
+          <t>Ram BazarSonipat SO</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Rania SO</t>
+          <t>Ram Pura Olony S.O</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Rathdhana Road Sonipat SO</t>
+          <t>Rania SO</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Rattia SO</t>
+          <t>Rathdhana Road Sonipat SO</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Refinery Township Panipat SO</t>
+          <t>Rattia SO</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Rewari SO</t>
+          <t>Refinery Township Panipat SO</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Rodhan SO</t>
+          <t>Rewari SO</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Rohat SO Sonipat</t>
+          <t>Rodhan SO</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Rohtak HO</t>
+          <t>Rohat SO Sonipat</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Rohtak Sector I SO</t>
+          <t>Rohtak HO</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Rohtak Town SO</t>
+          <t>Rohtak Sector I SO</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>S.S. Kunjpura S.O</t>
+          <t>Rohtak Town SO</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SECTOR46</t>
+          <t>S.S. Kunjpura S.O</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Sadar Bazar S.O (Ambala)</t>
+          <t>SECTOR46</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Sadhaura S.O</t>
+          <t>Sadar Bazar S.O (Ambala)</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Safidon City S.O</t>
+          <t>Sadhaura S.O</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Safidon S.O</t>
+          <t>Safidon City S.O</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Saha S.O</t>
+          <t>Safidon S.O</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Sahlawas SO</t>
+          <t>Saha S.O</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Salwan S.O</t>
+          <t>Sahlawas SO</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Samalkha S.O</t>
+          <t>Salwan S.O</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Sampla SO</t>
+          <t>Samalkha S.O</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Sanghi SO</t>
+          <t>Sampla SO</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -9628,7 +9628,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Sanwar SO Bhiwani</t>
+          <t>Sanghi SO</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -9649,7 +9649,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Saraswati Mandir Pehowa S.O</t>
+          <t>Sanwar SO Bhiwani</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Saraswati Nagar S.O</t>
+          <t>Saraswati Mandir Pehowa S.O</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Sarawan S.O</t>
+          <t>Saraswati Nagar S.O</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Satroad Khurd SO</t>
+          <t>Sarawan S.O</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Sec91 SO</t>
+          <t>Satroad Khurd SO</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Sector 15 Panchkula S.O</t>
+          <t>Sec91 SO</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Sector 20 Panchkula S.O</t>
+          <t>Sector 15 Panchkula S.O</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Sector 26 Panchkula S.O</t>
+          <t>Sector 20 Panchkula S.O</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Sector 3 U E KKR S.O</t>
+          <t>Sector 26 Panchkula S.O</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Sector 4 Karnal S.O</t>
+          <t>Sector 3 U E KKR S.O</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Sector 8 Karnal S.O</t>
+          <t>Sector 4 Karnal S.O</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Sector21D  SO</t>
+          <t>Sector 8 Karnal S.O</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Sector55 PO</t>
+          <t>Sector21D  SO</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Shahabad(M) S.O</t>
+          <t>Sector55 PO</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Shahzadpur S.O.</t>
+          <t>Shahabad(M) S.O</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Shamlo Kalan S.O</t>
+          <t>Shahzadpur S.O.</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -9985,7 +9985,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Shivaji Colony SO</t>
+          <t>Shamlo Kalan S.O</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -10006,7 +10006,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Shivaji Nagar SO Gurgaon</t>
+          <t>Shivaji Colony SO</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Sikander Pur SO</t>
+          <t>Shivaji Nagar SO Gurgaon</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Siri Jiwan Nagar SO</t>
+          <t>Sikander Pur SO</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Sirsa HO</t>
+          <t>Siri Jiwan Nagar SO</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Sisai SO Hisar</t>
+          <t>Sirsa HO</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Siwan Gate Kaithal S.O</t>
+          <t>Sisai SO Hisar</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Siwan S.O</t>
+          <t>Siwan Gate Kaithal S.O</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Siwani SO</t>
+          <t>Siwan S.O</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Sohna SO</t>
+          <t>Siwani SO</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Sonipat HO</t>
+          <t>Sohna SO</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Sonipat Kty SO</t>
+          <t>Sonipat HO</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Sonipat Mandi SO</t>
+          <t>Sonipat Kty SO</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -10258,7 +10258,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Sonipat Sector 14 SO</t>
+          <t>Sonipat Mandi SO</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Subzi  Mandi S.O</t>
+          <t>Sonipat Sector 14 SO</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Surajkund Faridabad SO</t>
+          <t>Subzi  Mandi S.O</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Taraori S.O</t>
+          <t>Surajkund Faridabad SO</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -10342,7 +10342,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Taroari Mandi S.O</t>
+          <t>Taraori S.O</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Tauru SO</t>
+          <t>Taroari Mandi S.O</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Tehsil Road Rewari SO</t>
+          <t>Tauru SO</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Thanesar Town S.O</t>
+          <t>Tehsil Road Rewari SO</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Thermal Colony Yamuna Nagar S.O</t>
+          <t>Thanesar Town S.O</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Thol S.O</t>
+          <t>Thermal Colony Yamuna Nagar S.O</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Tigaon SO</t>
+          <t>Thol S.O</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -10489,7 +10489,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Tigrana SO</t>
+          <t>Tigaon SO</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Tohana Mandi SO</t>
+          <t>Tigrana SO</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Tohana SO</t>
+          <t>Tohana Mandi SO</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -10552,7 +10552,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Top Khana Bazar S.O</t>
+          <t>Tohana SO</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -10573,7 +10573,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Tosham SO</t>
+          <t>Top Khana Bazar S.O</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Uchana S.O</t>
+          <t>Tosham SO</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -10615,7 +10615,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Uklana Mandi SO</t>
+          <t>Total:</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Urban Estate  2 Hisar SO</t>
+          <t>Uchana S.O</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -10657,7 +10657,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Urban Estate Gurgaon SO</t>
+          <t>Uklana Mandi SO</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Vatika India Sec 82 SO</t>
+          <t>Urban Estate  2 Hisar SO</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Vidut Nagar Hisar SO</t>
+          <t>Urban Estate Gurgaon SO</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -10720,16 +10720,58 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
+          <t>Vatika India Sec 82 SO</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>0</v>
+      </c>
+      <c r="D491" t="n">
+        <v>0</v>
+      </c>
+      <c r="E491" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Vidut Nagar Hisar SO</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>0</v>
+      </c>
+      <c r="D492" t="n">
+        <v>0</v>
+      </c>
+      <c r="E492" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
           <t>Yamunanagar H.O</t>
         </is>
       </c>
-      <c r="C491" t="n">
-        <v>0</v>
-      </c>
-      <c r="D491" t="n">
-        <v>0</v>
-      </c>
-      <c r="E491" t="n">
+      <c r="C493" t="n">
+        <v>0</v>
+      </c>
+      <c r="D493" t="n">
+        <v>0</v>
+      </c>
+      <c r="E493" t="n">
         <v>0</v>
       </c>
     </row>
